--- a/public/Journey Novembro 2026 - Opcao 2.xlsx
+++ b/public/Journey Novembro 2026 - Opcao 2.xlsx
@@ -8100,7 +8100,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>S00170 - UNIAR - AVENIDA. AYRTON SENNA - 1.850 - RIO DE JANEIRO - RJ</t>
+          <t>S06150 - FRIGELAR - AVENIDA AYRTON SENNA - 4701 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>UNIAR</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>S00141 - UNIAR - RUA MARIZ E BARROS - 521 - NITEROI - RJ</t>
+          <t>S00164 - CLIMA RIO - RUA MANOEL JOAO GONCALVES - 84 - SAO GONCALO - RJ</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>UNIAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>NITEROI</t>
+          <t>SAO GONCALO</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>S00170 - UNIAR - AVENIDA. AYRTON SENNA - 1.850 - RIO DE JANEIRO - RJ</t>
+          <t>S06150 - FRIGELAR - AVENIDA AYRTON SENNA - 4701 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>UNIAR</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>S00141 - UNIAR - RUA MARIZ E BARROS - 521 - NITEROI - RJ</t>
+          <t>S00164 - CLIMA RIO - RUA MANOEL JOAO GONCALVES - 84 - SAO GONCALO - RJ</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -9988,12 +9988,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>UNIAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>NITEROI</t>
+          <t>SAO GONCALO</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>S00170 - UNIAR - AVENIDA. AYRTON SENNA - 1.850 - RIO DE JANEIRO - RJ</t>
+          <t>S06150 - FRIGELAR - AVENIDA AYRTON SENNA - 4701 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>UNIAR</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>S00148 - UNIAR - R. DOM PEDRO II - 390 - PORTO ALEGRE - RS</t>
+          <t>S01271 - FRIGELAR - AVENIDA PERNAMBUCO - 2273 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>UNIAR</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>S00229 - UNIAR - RUA PROFESSOR CRISTIANO FISCHER - 1400 - PORTO ALEGRE - RS</t>
+          <t>S00119 - FRIGELAR - AVENIDA PERNAMBUCO - 2285 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>UNIAR</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>S00148 - UNIAR - R. DOM PEDRO II - 390 - PORTO ALEGRE - RS</t>
+          <t>S15962 - HAVAN - RUA OTAVIO SCHEMES - 4105 - GRAVATAI - RS</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -12040,12 +12040,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>UNIAR</t>
+          <t>HAVAN</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>GRAVATAI</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>S00229 - UNIAR - RUA PROFESSOR CRISTIANO FISCHER - 1400 - PORTO ALEGRE - RS</t>
+          <t>S18040 - HAVAN - AVENIDA ASSIS BRASIL - 11120 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>UNIAR</t>
+          <t>HAVAN</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>S00148 - UNIAR - R. DOM PEDRO II - 390 - PORTO ALEGRE - RS</t>
+          <t>S01271 - FRIGELAR - AVENIDA PERNAMBUCO - 2273 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>UNIAR</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>S00229 - UNIAR - RUA PROFESSOR CRISTIANO FISCHER - 1400 - PORTO ALEGRE - RS</t>
+          <t>S00119 - FRIGELAR - AVENIDA PERNAMBUCO - 2285 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>UNIAR</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -13012,7 +13012,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>S00148 - UNIAR - R. DOM PEDRO II - 390 - PORTO ALEGRE - RS</t>
+          <t>S15962 - HAVAN - RUA OTAVIO SCHEMES - 4105 - GRAVATAI - RS</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -13657,12 +13657,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>UNIAR</t>
+          <t>HAVAN</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>GRAVATAI</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>S00229 - UNIAR - RUA PROFESSOR CRISTIANO FISCHER - 1400 - PORTO ALEGRE - RS</t>
+          <t>S18040 - HAVAN - AVENIDA ASSIS BRASIL - 11120 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -13744,7 +13744,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>UNIAR</t>
+          <t>HAVAN</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>S00901 - UNIAR - AV. DOUTOR CARLOS DE MORAES BARROS - 350 - OSASCO - SP</t>
+          <t>S06664 - FRIGELAR - AVENIDA PROF FRANCISCO MORATO - 3205 - SAO PAULO - SP</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -14839,12 +14839,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>UNIAR</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>OSASCO</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>S01983 - UNIAR - AVENIDA SUPLICY - 443 - GUARULHOS - SP</t>
+          <t>S04610 - FRIGELAR - AVENIDA MONTEIRO LOBATO - 393 - GUARULHOS - SP</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>UNIAR</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>S00146 - UNIAR - RUA BARAO DE CAMPINAS - 690 - SAO PAULO - SP</t>
+          <t>S02324 - FRIGELAR - ALAMEDA GLETE - 908 - SAO PAULO - SP</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>UNIAR</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -16707,7 +16707,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>S01983 - UNIAR - AVENIDA SUPLICY - 443 - GUARULHOS - SP</t>
+          <t>S04610 - FRIGELAR - AVENIDA MONTEIRO LOBATO - 393 - GUARULHOS - SP</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -16717,7 +16717,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>UNIAR</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -16881,7 +16881,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>S00146 - UNIAR - RUA BARAO DE CAMPINAS - 690 - SAO PAULO - SP</t>
+          <t>S02324 - FRIGELAR - ALAMEDA GLETE - 908 - SAO PAULO - SP</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -16891,7 +16891,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>UNIAR</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -16906,7 +16906,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>S00901 - UNIAR - AV. DOUTOR CARLOS DE MORAES BARROS - 350 - OSASCO - SP</t>
+          <t>S06664 - FRIGELAR - AVENIDA PROF FRANCISCO MORATO - 3205 - SAO PAULO - SP</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -17326,12 +17326,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>UNIAR</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>OSASCO</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">

--- a/public/Journey Novembro 2026 - Opcao 2.xlsx
+++ b/public/Journey Novembro 2026 - Opcao 2.xlsx
@@ -517,12 +517,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Finados</t>
+          <t>Feriado Nacional - Finados</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -568,12 +568,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>S04297 - FRIGELAR - RUA ROMUALDO ANDREAZZI - 492 - CAMPINAS - SP</t>
+          <t>S00976 - FRIGELAR - RUA HORTENCIO RIBEIRO DE LUNA - 1841 - JOAO PESSOA - PB</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -603,27 +603,27 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>CAMPINAS</t>
+          <t>JOAO PESSOA</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>20 min (8 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>20 min (8 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Viagem</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>S03839 - CLIMA RIO - AVENIDA GOVERNADOR PEDRO TOLEDO - 671 - CAMPINAS - SP</t>
+          <t>S00309 - MAGNO - RODOVIA BR 230 -  CABEDELO - PB</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -685,32 +685,32 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>MAGNO</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CAMPINAS</t>
+          <t>CABEDELO</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>15 min (5 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>15 min (5 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Viagem</t>
         </is>
       </c>
     </row>
@@ -742,12 +742,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>S05854 - FRIGELAR - AVENIDA GENERAL CARNEIRO - 914 - SOROCABA - SP</t>
+          <t>S00986 - FRIOPECAS - IMBIRIBEIRA - PE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -772,32 +772,32 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>FRIOPECAS</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>SOROCABA</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1h15 (88 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1h15 (88 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>S01623 - CLIMA RIO - RUA COMENDADOR OTTERER - 563 - SOROCABA - SP</t>
+          <t>S00623 - FRIGELAR - RUA SGTO SILVIO D HOLLEMBACH - 171 - IMBIRIBEIRA - PE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -859,32 +859,32 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>SOROCABA</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>15 min (6 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>15 min (6 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>S04530 - FRIGELAR - AVENIDA DOUTOR PAULO DE MORAES - 1111 - PIRACICABA - SP</t>
+          <t>S01960 - FERREIRA COSTA - AVENIDA MAL. MASCARENHAS DE MORAIS - 2967 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -946,42 +946,42 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>FERREIRA COSTA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PIRACICABA</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>55 min (67 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>55 min (67 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>S00156 - CENTRAL AR - R. GERSON MENDES - 102 - ITU - SP</t>
+          <t>S01119 - CLIMA RIO - RUA ARTUR MOURA - 91 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1033,37 +1033,37 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CENTRAL AR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ITU</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1h15 (98 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1h15 (98 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>S03839 - CLIMA RIO - AVENIDA GOVERNADOR PEDRO TOLEDO - 671 - CAMPINAS - SP</t>
+          <t>S04106 - FRIGELAR - AVENIDA ENG DOMINGOS FERREIRA - 2030 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1120,17 +1120,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>CAMPINAS</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>15 min (5 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>15 min (5 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>S04297 - FRIGELAR - RUA ROMUALDO ANDREAZZI - 492 - CAMPINAS - SP</t>
+          <t>S00483 - FERREIRA COSTA - R. CONEGO BARATA - 275 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>FERREIRA COSTA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>CAMPINAS</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>15 min (5 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>15 min (5 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1264,12 +1264,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>S01623 - CLIMA RIO - RUA COMENDADOR OTTERER - 563 - SOROCABA - SP</t>
+          <t>S04106 - FRIGELAR - AVENIDA ENG DOMINGOS FERREIRA - 2030 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>SOROCABA</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1h15 (88 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1h15 (88 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>S05854 - FRIGELAR - AVENIDA GENERAL CARNEIRO - 914 - SOROCABA - SP</t>
+          <t>S03596 - CLIMA RIO - AV. ENG. DOMINGOS FERREIRA - 1274 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1381,17 +1381,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>SOROCABA</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>15 min (6 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>15 min (6 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>S04297 - FRIGELAR - RUA ROMUALDO ANDREAZZI - 492 - CAMPINAS - SP</t>
+          <t>S02677 - FRIGELAR - AVENIDA PRESIDENTE EPITACIO PESSOA - 821 - JOAO PESSOA - PB</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1473,27 +1473,27 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>CAMPINAS</t>
+          <t>JOAO PESSOA</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>20 min (8 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>20 min (8 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Viagem</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>S03839 - CLIMA RIO - AVENIDA GOVERNADOR PEDRO TOLEDO - 671 - CAMPINAS - SP</t>
+          <t>S04649 - CLIMA RIO - AVENIDA PRESIDENTE EPITACIO PESSOA - 941 - JOAO PESSOA - PB</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1560,27 +1560,27 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>CAMPINAS</t>
+          <t>JOAO PESSOA</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>15 min (5 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>15 min (5 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Viagem</t>
         </is>
       </c>
     </row>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>S01963 - CENTRAL AR - AVENIDA. BRASILIA - 2121 - ARACATUBA - SP</t>
+          <t>S00986 - FRIOPECAS - IMBIRIBEIRA - PE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1642,47 +1642,47 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CENTRAL AR</t>
+          <t>FRIOPECAS</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>ARACATUBA</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Voo Aéreo / Deslocamento Local (5 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Voo Aéreo / Deslocamento Local (5 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Viagem</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1699,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>S00156 - CENTRAL AR - RUA DO FICO - 211 - ARACATUBA - SP</t>
+          <t>S00623 - FRIGELAR - RUA SGTO SILVIO D HOLLEMBACH - 171 - IMBIRIBEIRA - PE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1729,47 +1729,47 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CENTRAL AR</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>ARACATUBA</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>10 min (4 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>10 min (4 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Viagem</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -1786,12 +1786,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>S03162 - CLIMA RIO - AVENIDA DOUTOR FRANCISCO JUNQUEIRA - 851 - RIBEIRAO PRETO - SP</t>
+          <t>S01960 - FERREIRA COSTA - AVENIDA MAL. MASCARENHAS DE MORAIS - 2967 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>FERREIRA COSTA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>RIBEIRAO PRETO</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1836,22 +1836,22 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2h10 (173 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2h10 (173 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>S00704 - FRIGELAR - RUA VISCONDE DO RIO BRANCO - 1151 - RIBEIRAO PRETO - SP</t>
+          <t>S01119 - CLIMA RIO - RUA ARTUR MOURA - 91 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>RIBEIRAO PRETO</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1923,17 +1923,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>10 min (2 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>10 min (2 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>S00156 - CENTRAL AR - R. GERSON MENDES - 102 - ITU - SP</t>
+          <t>S04106 - FRIGELAR - AVENIDA ENG DOMINGOS FERREIRA - 2030 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1990,42 +1990,42 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CENTRAL AR</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ITU</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>45 min (52 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>45 min (52 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>S04297 - FRIGELAR - RUA ROMUALDO ANDREAZZI - 492 - CAMPINAS - SP</t>
+          <t>S00483 - FERREIRA COSTA - R. CONEGO BARATA - 275 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>FERREIRA COSTA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>CAMPINAS</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>45 min (52 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>45 min (52 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>S01623 - CLIMA RIO - RUA COMENDADOR OTTERER - 563 - SOROCABA - SP</t>
+          <t>S04106 - FRIGELAR - AVENIDA ENG DOMINGOS FERREIRA - 2030 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2164,22 +2164,22 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>SOROCABA</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>S05854 - FRIGELAR - AVENIDA GENERAL CARNEIRO - 914 - SOROCABA - SP</t>
+          <t>S03596 - CLIMA RIO - AV. ENG. DOMINGOS FERREIRA - 1274 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2251,22 +2251,22 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>SOROCABA</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>S04297 - FRIGELAR - RUA ROMUALDO ANDREAZZI - 492 - CAMPINAS - SP</t>
+          <t>S00986 - FRIOPECAS - IMBIRIBEIRA - PE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2338,32 +2338,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>FRIOPECAS</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>CAMPINAS</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>20 min (8 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>20 min (8 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>S03839 - CLIMA RIO - AVENIDA GOVERNADOR PEDRO TOLEDO - 671 - CAMPINAS - SP</t>
+          <t>S00623 - FRIGELAR - RUA SGTO SILVIO D HOLLEMBACH - 171 - IMBIRIBEIRA - PE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2425,32 +2425,32 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>CAMPINAS</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>15 min (5 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>15 min (5 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>S04297 - FRIGELAR - RUA ROMUALDO ANDREAZZI - 492 - CAMPINAS - SP</t>
+          <t>S00986 - FRIOPECAS - IMBIRIBEIRA - PE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2512,32 +2512,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>FRIOPECAS</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>CAMPINAS</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>20 min (8 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>20 min (8 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>S03839 - CLIMA RIO - AVENIDA GOVERNADOR PEDRO TOLEDO - 671 - CAMPINAS - SP</t>
+          <t>S00623 - FRIGELAR - RUA SGTO SILVIO D HOLLEMBACH - 171 - IMBIRIBEIRA - PE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2599,32 +2599,32 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>CAMPINAS</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>15 min (5 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>15 min (5 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>S05854 - FRIGELAR - AVENIDA GENERAL CARNEIRO - 914 - SOROCABA - SP</t>
+          <t>S01960 - FERREIRA COSTA - AVENIDA MAL. MASCARENHAS DE MORAIS - 2967 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2686,17 +2686,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>FERREIRA COSTA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>SOROCABA</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1h15 (88 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1h15 (88 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2743,12 +2743,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>S01623 - CLIMA RIO - RUA COMENDADOR OTTERER - 563 - SOROCABA - SP</t>
+          <t>S01119 - CLIMA RIO - RUA ARTUR MOURA - 91 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>SOROCABA</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>15 min (6 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>15 min (6 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dia da Consciência Negra</t>
+          <t>Feriado Nacional - Dia da Consciência Negra</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>S00704 - FRIGELAR - RUA VISCONDE DO RIO BRANCO - 1151 - RIBEIRAO PRETO - SP</t>
+          <t>S04106 - FRIGELAR - AVENIDA ENG DOMINGOS FERREIRA - 2030 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>RIBEIRAO PRETO</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2931,22 +2931,22 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2h10 (173 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2h10 (173 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>S03162 - CLIMA RIO - AVENIDA DOUTOR FRANCISCO JUNQUEIRA - 851 - RIBEIRAO PRETO - SP</t>
+          <t>S03596 - CLIMA RIO - AV. ENG. DOMINGOS FERREIRA - 1274 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>RIBEIRAO PRETO</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10 min (2 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>10 min (2 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>S04297 - FRIGELAR - RUA ROMUALDO ANDREAZZI - 492 - CAMPINAS - SP</t>
+          <t>S00986 - FRIOPECAS - IMBIRIBEIRA - PE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3085,32 +3085,32 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>FRIOPECAS</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>CAMPINAS</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>20 min (8 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>20 min (8 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>S03839 - CLIMA RIO - AVENIDA GOVERNADOR PEDRO TOLEDO - 671 - CAMPINAS - SP</t>
+          <t>S00483 - FERREIRA COSTA - R. CONEGO BARATA - 275 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3172,17 +3172,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>FERREIRA COSTA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>CAMPINAS</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>15 min (5 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>15 min (5 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>S05854 - FRIGELAR - AVENIDA GENERAL CARNEIRO - 914 - SOROCABA - SP</t>
+          <t>S00986 - FRIOPECAS - IMBIRIBEIRA - PE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3259,32 +3259,32 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>FRIOPECAS</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>SOROCABA</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1h15 (88 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1h15 (88 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>S01623 - CLIMA RIO - RUA COMENDADOR OTTERER - 563 - SOROCABA - SP</t>
+          <t>S00623 - FRIGELAR - RUA SGTO SILVIO D HOLLEMBACH - 171 - IMBIRIBEIRA - PE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3346,32 +3346,32 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>SOROCABA</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>15 min (6 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>15 min (6 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>S04530 - FRIGELAR - AVENIDA DOUTOR PAULO DE MORAES - 1111 - PIRACICABA - SP</t>
+          <t>S01960 - FERREIRA COSTA - AVENIDA MAL. MASCARENHAS DE MORAIS - 2967 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3433,42 +3433,42 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>FERREIRA COSTA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PIRACICABA</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>55 min (67 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>55 min (67 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>S03839 - CLIMA RIO - AVENIDA GOVERNADOR PEDRO TOLEDO - 671 - CAMPINAS - SP</t>
+          <t>S01119 - CLIMA RIO - RUA ARTUR MOURA - 91 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>CAMPINAS</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3540,17 +3540,17 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>55 min (67 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>55 min (67 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3577,12 +3577,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>S01623 - CLIMA RIO - RUA COMENDADOR OTTERER - 563 - SOROCABA - SP</t>
+          <t>S04106 - FRIGELAR - AVENIDA ENG DOMINGOS FERREIRA - 2030 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3607,17 +3607,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SOROCABA</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1h15 (88 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1h15 (88 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>S05854 - FRIGELAR - AVENIDA GENERAL CARNEIRO - 914 - SOROCABA - SP</t>
+          <t>S00483 - FERREIRA COSTA - R. CONEGO BARATA - 275 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3694,17 +3694,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>FERREIRA COSTA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>SOROCABA</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>15 min (6 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>15 min (6 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>S05854 - FRIGELAR - AVENIDA GENERAL CARNEIRO - 914 - SOROCABA - SP</t>
+          <t>S04106 - FRIGELAR - AVENIDA ENG DOMINGOS FERREIRA - 2030 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>SOROCABA</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1h15 (88 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1h15 (88 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SPI_1</t>
+          <t>NE_2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>S01623 - CLIMA RIO - RUA COMENDADOR OTTERER - 563 - SOROCABA - SP</t>
+          <t>S03596 - CLIMA RIO - AV. ENG. DOMINGOS FERREIRA - 1274 - RECIFE - PE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>SOROCABA</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>15 min (6 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>15 min (6 km)</t>
+          <t>35 min</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>S00976 - FRIGELAR - RUA HORTENCIO RIBEIRO DE LUNA - 1841 - JOAO PESSOA - PB</t>
+          <t>S07202 - FRIGELAR - AVENIDA INCONFIDENCIA - 31 - CANOAS - RS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>JOAO PESSOA</t>
+          <t>CANOAS</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Viagem</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -4063,12 +4063,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>S00309 - MAGNO - RODOVIA BR 230 -  CABEDELO - PB</t>
+          <t>S19798 - HAVAN - AV FARROUPILHA - 4707 - CANOAS - RS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4093,22 +4093,22 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>MAGNO</t>
+          <t>HAVAN</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>CABEDELO</t>
+          <t>CANOAS</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Viagem</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>S00986 - FRIOPECAS - IMBIRIBEIRA - PE</t>
+          <t>S00119 - FRIGELAR - AVENIDA PERNAMBUCO - 2285 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4180,22 +4180,22 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>S00623 - FRIGELAR - RUA SGTO SILVIO D HOLLEMBACH - 171 - IMBIRIBEIRA - PE</t>
+          <t>S00127 - WEBCONTINENTAL - TRAVENIDAESSA VENEZUELA 210 NAVENIDAEGANTES - SN - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4267,22 +4267,22 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>WEBCONTINENTAL</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>S01960 - FERREIRA COSTA - AVENIDA MAL. MASCARENHAS DE MORAIS - 2967 - RECIFE - PE</t>
+          <t>S01271 - FRIGELAR - AVENIDA PERNAMBUCO - 2273 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4354,17 +4354,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>FERREIRA COSTA</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>S01119 - CLIMA RIO - RUA ARTUR MOURA - 91 - RECIFE - PE</t>
+          <t>S00119 - FRIGELAR - AVENIDA PERNAMBUCO - 2285 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4441,17 +4441,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>S04106 - FRIGELAR - AVENIDA ENG DOMINGOS FERREIRA - 2030 - RECIFE - PE</t>
+          <t>S18040 - HAVAN - AVENIDA ASSIS BRASIL - 11120 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4528,22 +4528,22 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>HAVAN</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4585,12 +4585,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>S00483 - FERREIRA COSTA - R. CONEGO BARATA - 275 - RECIFE - PE</t>
+          <t>S07717 - FRIGELAR - RUA VINTE E CINCO DE JULHO - 536 - NOVO HAMBURGO - RS</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4615,22 +4615,22 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>FERREIRA COSTA</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>NOVO HAMBURGO</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>S04106 - FRIGELAR - AVENIDA ENG DOMINGOS FERREIRA - 2030 - RECIFE - PE</t>
+          <t>S01271 - FRIGELAR - AVENIDA PERNAMBUCO - 2273 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4707,12 +4707,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>S03596 - CLIMA RIO - AV. ENG. DOMINGOS FERREIRA - 1274 - RECIFE - PE</t>
+          <t>S02352 - CLIMA RIO - AVENIDA FRANCA - 606 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4794,17 +4794,17 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4846,12 +4846,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>S02677 - FRIGELAR - AVENIDA PRESIDENTE EPITACIO PESSOA - 821 - JOAO PESSOA - PB</t>
+          <t>S07202 - FRIGELAR - AVENIDA INCONFIDENCIA - 31 - CANOAS - RS</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4881,17 +4881,17 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>JOAO PESSOA</t>
+          <t>CANOAS</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>Viagem</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -4933,12 +4933,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>S04649 - CLIMA RIO - AVENIDA PRESIDENTE EPITACIO PESSOA - 941 - JOAO PESSOA - PB</t>
+          <t>S19798 - HAVAN - AV FARROUPILHA - 4707 - CANOAS - RS</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4963,22 +4963,22 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>HAVAN</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>JOAO PESSOA</t>
+          <t>CANOAS</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>Viagem</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -5020,12 +5020,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>S00986 - FRIOPECAS - IMBIRIBEIRA - PE</t>
+          <t>S00119 - FRIGELAR - AVENIDA PERNAMBUCO - 2285 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5050,22 +5050,22 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>S00623 - FRIGELAR - RUA SGTO SILVIO D HOLLEMBACH - 171 - IMBIRIBEIRA - PE</t>
+          <t>S00127 - WEBCONTINENTAL - TRAVENIDAESSA VENEZUELA 210 NAVENIDAEGANTES - SN - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5137,22 +5137,22 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>WEBCONTINENTAL</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5194,12 +5194,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>S01960 - FERREIRA COSTA - AVENIDA MAL. MASCARENHAS DE MORAIS - 2967 - RECIFE - PE</t>
+          <t>S15962 - HAVAN - RUA OTAVIO SCHEMES - 4105 - GRAVATAI - RS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5224,22 +5224,22 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>FERREIRA COSTA</t>
+          <t>HAVAN</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>GRAVATAI</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>S01119 - CLIMA RIO - RUA ARTUR MOURA - 91 - RECIFE - PE</t>
+          <t>S18040 - HAVAN - AVENIDA ASSIS BRASIL - 11120 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5311,22 +5311,22 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>HAVAN</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>S04106 - FRIGELAR - AVENIDA ENG DOMINGOS FERREIRA - 2030 - RECIFE - PE</t>
+          <t>S18040 - HAVAN - AVENIDA ASSIS BRASIL - 11120 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5398,22 +5398,22 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>HAVAN</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>S00483 - FERREIRA COSTA - R. CONEGO BARATA - 275 - RECIFE - PE</t>
+          <t>S07717 - FRIGELAR - RUA VINTE E CINCO DE JULHO - 536 - NOVO HAMBURGO - RS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5485,22 +5485,22 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>FERREIRA COSTA</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>NOVO HAMBURGO</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>S04106 - FRIGELAR - AVENIDA ENG DOMINGOS FERREIRA - 2030 - RECIFE - PE</t>
+          <t>S01271 - FRIGELAR - AVENIDA PERNAMBUCO - 2273 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5629,12 +5629,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>S03596 - CLIMA RIO - AV. ENG. DOMINGOS FERREIRA - 1274 - RECIFE - PE</t>
+          <t>S02352 - CLIMA RIO - AVENIDA FRANCA - 606 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5664,17 +5664,17 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>S00986 - FRIOPECAS - IMBIRIBEIRA - PE</t>
+          <t>S07202 - FRIGELAR - AVENIDA INCONFIDENCIA - 31 - CANOAS - RS</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5746,17 +5746,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>CANOAS</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>S00623 - FRIGELAR - RUA SGTO SILVIO D HOLLEMBACH - 171 - IMBIRIBEIRA - PE</t>
+          <t>S19798 - HAVAN - AV FARROUPILHA - 4707 - CANOAS - RS</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5833,22 +5833,22 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>HAVAN</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>CANOAS</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>S00986 - FRIOPECAS - IMBIRIBEIRA - PE</t>
+          <t>S00119 - FRIGELAR - AVENIDA PERNAMBUCO - 2285 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5920,22 +5920,22 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>S00623 - FRIGELAR - RUA SGTO SILVIO D HOLLEMBACH - 171 - IMBIRIBEIRA - PE</t>
+          <t>S00127 - WEBCONTINENTAL - TRAVENIDAESSA VENEZUELA 210 NAVENIDAEGANTES - SN - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6007,22 +6007,22 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>WEBCONTINENTAL</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>S01960 - FERREIRA COSTA - AVENIDA MAL. MASCARENHAS DE MORAIS - 2967 - RECIFE - PE</t>
+          <t>S01271 - FRIGELAR - AVENIDA PERNAMBUCO - 2273 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6094,17 +6094,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>FERREIRA COSTA</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>S01119 - CLIMA RIO - RUA ARTUR MOURA - 91 - RECIFE - PE</t>
+          <t>S00119 - FRIGELAR - AVENIDA PERNAMBUCO - 2285 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6181,17 +6181,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6289,12 +6289,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>S04106 - FRIGELAR - AVENIDA ENG DOMINGOS FERREIRA - 2030 - RECIFE - PE</t>
+          <t>S01271 - FRIGELAR - AVENIDA PERNAMBUCO - 2273 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>S03596 - CLIMA RIO - AV. ENG. DOMINGOS FERREIRA - 1274 - RECIFE - PE</t>
+          <t>S02352 - CLIMA RIO - AVENIDA FRANCA - 606 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6411,17 +6411,17 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>S00986 - FRIOPECAS - IMBIRIBEIRA - PE</t>
+          <t>S07202 - FRIGELAR - AVENIDA INCONFIDENCIA - 31 - CANOAS - RS</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6493,17 +6493,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>CANOAS</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>S00483 - FERREIRA COSTA - R. CONEGO BARATA - 275 - RECIFE - PE</t>
+          <t>S19798 - HAVAN - AV FARROUPILHA - 4707 - CANOAS - RS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6580,22 +6580,22 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>FERREIRA COSTA</t>
+          <t>HAVAN</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>CANOAS</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>S00986 - FRIOPECAS - IMBIRIBEIRA - PE</t>
+          <t>S00119 - FRIGELAR - AVENIDA PERNAMBUCO - 2285 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6667,22 +6667,22 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>S00623 - FRIGELAR - RUA SGTO SILVIO D HOLLEMBACH - 171 - IMBIRIBEIRA - PE</t>
+          <t>S00127 - WEBCONTINENTAL - TRAVENIDAESSA VENEZUELA 210 NAVENIDAEGANTES - SN - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6754,22 +6754,22 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>WEBCONTINENTAL</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>S01960 - FERREIRA COSTA - AVENIDA MAL. MASCARENHAS DE MORAIS - 2967 - RECIFE - PE</t>
+          <t>S15962 - HAVAN - RUA OTAVIO SCHEMES - 4105 - GRAVATAI - RS</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6841,22 +6841,22 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>FERREIRA COSTA</t>
+          <t>HAVAN</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>GRAVATAI</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>S01119 - CLIMA RIO - RUA ARTUR MOURA - 91 - RECIFE - PE</t>
+          <t>S18040 - HAVAN - AVENIDA ASSIS BRASIL - 11120 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6928,22 +6928,22 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>HAVAN</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6985,12 +6985,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>S04106 - FRIGELAR - AVENIDA ENG DOMINGOS FERREIRA - 2030 - RECIFE - PE</t>
+          <t>S18040 - HAVAN - AVENIDA ASSIS BRASIL - 11120 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7015,22 +7015,22 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>HAVAN</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>S00483 - FERREIRA COSTA - R. CONEGO BARATA - 275 - RECIFE - PE</t>
+          <t>S07717 - FRIGELAR - RUA VINTE E CINCO DE JULHO - 536 - NOVO HAMBURGO - RS</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7102,22 +7102,22 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>FERREIRA COSTA</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>NOVO HAMBURGO</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>S04106 - FRIGELAR - AVENIDA ENG DOMINGOS FERREIRA - 2030 - RECIFE - PE</t>
+          <t>S01271 - FRIGELAR - AVENIDA PERNAMBUCO - 2273 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NE_2</t>
+          <t>SUL_1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>S03596 - CLIMA RIO - AV. ENG. DOMINGOS FERREIRA - 1274 - RECIFE - PE</t>
+          <t>S02352 - CLIMA RIO - AVENIDA FRANCA - 606 - PORTO ALEGRE - RS</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7281,17 +7281,17 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Feriado Nacional - Finados</t>
+          <t>Finados</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7384,12 +7384,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>S04053 - CLIMA RIO - RUA MIGUEL DE FRIAS - 254 - NITEROI - RJ</t>
+          <t>S04297 - FRIGELAR - RUA ROMUALDO ANDREAZZI - 492 - CAMPINAS - SP</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -7414,17 +7414,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>NITEROI</t>
+          <t>CAMPINAS</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>20 min (8 km)</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>20 min (8 km)</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>S00164 - CLIMA RIO - RUA MANOEL JOAO GONCALVES - 84 - SAO GONCALO - RJ</t>
+          <t>S03839 - CLIMA RIO - AVENIDA GOVERNADOR PEDRO TOLEDO - 671 - CAMPINAS - SP</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7506,27 +7506,27 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>SAO GONCALO</t>
+          <t>CAMPINAS</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>S00633 - FRIOPECAS - RUA TEIXEIRA RIBEIRO - 275 - RIO DE JANEIRO - RJ</t>
+          <t>S05854 - FRIGELAR - AVENIDA GENERAL CARNEIRO - 914 - SOROCABA - SP</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7588,32 +7588,32 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>SOROCABA</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (88 km)</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (88 km)</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -7645,12 +7645,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>S05188 - FRIGELAR - RUA GUATEMALA - 371 - RIO DE JANEIRO - RJ</t>
+          <t>S01623 - CLIMA RIO - RUA COMENDADOR OTTERER - 563 - SOROCABA - SP</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7675,37 +7675,37 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>SOROCABA</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (6 km)</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (6 km)</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>S00895 - FRIGELAR - RUA GENERAL ARGOLO - 15 - SAO CRISTOVAO - RJ</t>
+          <t>S04530 - FRIGELAR - AVENIDA DOUTOR PAULO DE MORAES - 1111 - PIRACICABA - SP</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7767,27 +7767,27 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>PIRACICABA</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>55 min (67 km)</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>55 min (67 km)</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>S00228 - CLIMA RIO - AVENIDA LOBO JUNIOR - 1184 - RIO DE JANEIRO - RJ</t>
+          <t>S00156 - CENTRAL AR - R. GERSON MENDES - 102 - ITU - SP</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7849,37 +7849,37 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>CENTRAL AR</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>ITU</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (98 km)</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (98 km)</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -7906,12 +7906,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>S06150 - FRIGELAR - AVENIDA AYRTON SENNA - 4701 - RIO DE JANEIRO - RJ</t>
+          <t>S03839 - CLIMA RIO - AVENIDA GOVERNADOR PEDRO TOLEDO - 671 - CAMPINAS - SP</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7936,32 +7936,32 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>CAMPINAS</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>S00157 - CLIMA RIO - AVENIDA AYRTON SENNA - 1850 - RIO DE JANEIRO - RJ</t>
+          <t>S04297 - FRIGELAR - RUA ROMUALDO ANDREAZZI - 492 - CAMPINAS - SP</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8023,32 +8023,32 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>CAMPINAS</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>S06150 - FRIGELAR - AVENIDA AYRTON SENNA - 4701 - RIO DE JANEIRO - RJ</t>
+          <t>S01623 - CLIMA RIO - RUA COMENDADOR OTTERER - 563 - SOROCABA - SP</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8110,32 +8110,32 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>SOROCABA</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (88 km)</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (88 km)</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -8167,12 +8167,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>S00135 - CENTRAL AR - AV. DAS AMERICAS - 18000 - RIO DE JANEIRO - RJ</t>
+          <t>S05854 - FRIGELAR - AVENIDA GENERAL CARNEIRO - 914 - SOROCABA - SP</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8197,32 +8197,32 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>CENTRAL AR</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>SOROCABA</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (6 km)</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (6 km)</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>S04053 - CLIMA RIO - RUA MIGUEL DE FRIAS - 254 - NITEROI - RJ</t>
+          <t>S04297 - FRIGELAR - RUA ROMUALDO ANDREAZZI - 492 - CAMPINAS - SP</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -8284,17 +8284,17 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>NITEROI</t>
+          <t>CAMPINAS</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>20 min (8 km)</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>20 min (8 km)</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -8341,12 +8341,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>S00164 - CLIMA RIO - RUA MANOEL JOAO GONCALVES - 84 - SAO GONCALO - RJ</t>
+          <t>S03839 - CLIMA RIO - AVENIDA GOVERNADOR PEDRO TOLEDO - 671 - CAMPINAS - SP</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8376,27 +8376,27 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>SAO GONCALO</t>
+          <t>CAMPINAS</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>S00633 - FRIOPECAS - RUA TEIXEIRA RIBEIRO - 275 - RIO DE JANEIRO - RJ</t>
+          <t>S01963 - CENTRAL AR - AVENIDA. BRASILIA - 2121 - ARACATUBA - SP</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -8458,32 +8458,32 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>CENTRAL AR</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>ARACATUBA</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Voo Aéreo / Deslocamento Local (5 km)</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Voo Aéreo / Deslocamento Local (5 km)</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Viagem</t>
         </is>
       </c>
     </row>
@@ -8515,12 +8515,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>S05188 - FRIGELAR - RUA GUATEMALA - 371 - RIO DE JANEIRO - RJ</t>
+          <t>S00156 - CENTRAL AR - RUA DO FICO - 211 - ARACATUBA - SP</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -8545,37 +8545,37 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CENTRAL AR</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>ARACATUBA</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>10 min (4 km)</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>10 min (4 km)</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Viagem</t>
         </is>
       </c>
     </row>
@@ -8602,12 +8602,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>S00895 - FRIGELAR - RUA GENERAL ARGOLO - 15 - SAO CRISTOVAO - RJ</t>
+          <t>S03162 - CLIMA RIO - AVENIDA DOUTOR FRANCISCO JUNQUEIRA - 851 - RIBEIRAO PRETO - SP</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -8632,17 +8632,17 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>RIBEIRAO PRETO</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>2h10 (173 km)</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>2h10 (173 km)</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -8689,12 +8689,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>S00228 - CLIMA RIO - AVENIDA LOBO JUNIOR - 1184 - RIO DE JANEIRO - RJ</t>
+          <t>S00704 - FRIGELAR - RUA VISCONDE DO RIO BRANCO - 1151 - RIBEIRAO PRETO - SP</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -8719,17 +8719,17 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>RIBEIRAO PRETO</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -8739,17 +8739,17 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>10 min (2 km)</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>10 min (2 km)</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>S06150 - FRIGELAR - AVENIDA AYRTON SENNA - 4701 - RIO DE JANEIRO - RJ</t>
+          <t>S00156 - CENTRAL AR - R. GERSON MENDES - 102 - ITU - SP</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -8806,17 +8806,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CENTRAL AR</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>ITU</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>45 min (52 km)</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>45 min (52 km)</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -8863,12 +8863,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>S00157 - CLIMA RIO - AVENIDA AYRTON SENNA - 1850 - RIO DE JANEIRO - RJ</t>
+          <t>S04297 - FRIGELAR - RUA ROMUALDO ANDREAZZI - 492 - CAMPINAS - SP</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8893,32 +8893,32 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>CAMPINAS</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>45 min (52 km)</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>45 min (52 km)</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -8950,12 +8950,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>S06150 - FRIGELAR - AVENIDA AYRTON SENNA - 4701 - RIO DE JANEIRO - RJ</t>
+          <t>S01623 - CLIMA RIO - RUA COMENDADOR OTTERER - 563 - SOROCABA - SP</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -8980,17 +8980,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>SOROCABA</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>S00135 - CENTRAL AR - AV. DAS AMERICAS - 18000 - RIO DE JANEIRO - RJ</t>
+          <t>S05854 - FRIGELAR - AVENIDA GENERAL CARNEIRO - 914 - SOROCABA - SP</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -9067,17 +9067,17 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>CENTRAL AR</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>SOROCABA</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -9124,12 +9124,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>S04053 - CLIMA RIO - RUA MIGUEL DE FRIAS - 254 - NITEROI - RJ</t>
+          <t>S04297 - FRIGELAR - RUA ROMUALDO ANDREAZZI - 492 - CAMPINAS - SP</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9154,17 +9154,17 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>NITEROI</t>
+          <t>CAMPINAS</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>20 min (8 km)</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>20 min (8 km)</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -9211,12 +9211,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>S00164 - CLIMA RIO - RUA MANOEL JOAO GONCALVES - 84 - SAO GONCALO - RJ</t>
+          <t>S03839 - CLIMA RIO - AVENIDA GOVERNADOR PEDRO TOLEDO - 671 - CAMPINAS - SP</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9246,27 +9246,27 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>SAO GONCALO</t>
+          <t>CAMPINAS</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>S00633 - FRIOPECAS - RUA TEIXEIRA RIBEIRO - 275 - RIO DE JANEIRO - RJ</t>
+          <t>S04297 - FRIGELAR - RUA ROMUALDO ANDREAZZI - 492 - CAMPINAS - SP</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -9328,32 +9328,32 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>CAMPINAS</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>20 min (8 km)</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>20 min (8 km)</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -9385,12 +9385,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>S05188 - FRIGELAR - RUA GUATEMALA - 371 - RIO DE JANEIRO - RJ</t>
+          <t>S03839 - CLIMA RIO - AVENIDA GOVERNADOR PEDRO TOLEDO - 671 - CAMPINAS - SP</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -9415,37 +9415,37 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>CAMPINAS</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>S00895 - FRIGELAR - RUA GENERAL ARGOLO - 15 - SAO CRISTOVAO - RJ</t>
+          <t>S05854 - FRIGELAR - AVENIDA GENERAL CARNEIRO - 914 - SOROCABA - SP</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>SOROCABA</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (88 km)</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (88 km)</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>S00228 - CLIMA RIO - AVENIDA LOBO JUNIOR - 1184 - RIO DE JANEIRO - RJ</t>
+          <t>S01623 - CLIMA RIO - RUA COMENDADOR OTTERER - 563 - SOROCABA - SP</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>SOROCABA</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -9609,17 +9609,17 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (6 km)</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (6 km)</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -9646,12 +9646,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Feriado Nacional - Dia da Consciência Negra</t>
+          <t>Dia da Consciência Negra</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -9697,12 +9697,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>S06150 - FRIGELAR - AVENIDA AYRTON SENNA - 4701 - RIO DE JANEIRO - RJ</t>
+          <t>S00704 - FRIGELAR - RUA VISCONDE DO RIO BRANCO - 1151 - RIBEIRAO PRETO - SP</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -9732,27 +9732,27 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>RIBEIRAO PRETO</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>2h10 (173 km)</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>2h10 (173 km)</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -9784,12 +9784,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>S00157 - CLIMA RIO - AVENIDA AYRTON SENNA - 1850 - RIO DE JANEIRO - RJ</t>
+          <t>S03162 - CLIMA RIO - AVENIDA DOUTOR FRANCISCO JUNQUEIRA - 851 - RIBEIRAO PRETO - SP</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -9819,27 +9819,27 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>RIBEIRAO PRETO</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>10 min (2 km)</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>10 min (2 km)</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>S04053 - CLIMA RIO - RUA MIGUEL DE FRIAS - 254 - NITEROI - RJ</t>
+          <t>S04297 - FRIGELAR - RUA ROMUALDO ANDREAZZI - 492 - CAMPINAS - SP</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -9901,17 +9901,17 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>NITEROI</t>
+          <t>CAMPINAS</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>20 min (8 km)</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>20 min (8 km)</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -9958,12 +9958,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>S00164 - CLIMA RIO - RUA MANOEL JOAO GONCALVES - 84 - SAO GONCALO - RJ</t>
+          <t>S03839 - CLIMA RIO - AVENIDA GOVERNADOR PEDRO TOLEDO - 671 - CAMPINAS - SP</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -9993,27 +9993,27 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>SAO GONCALO</t>
+          <t>CAMPINAS</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>S00633 - FRIOPECAS - RUA TEIXEIRA RIBEIRO - 275 - RIO DE JANEIRO - RJ</t>
+          <t>S05854 - FRIGELAR - AVENIDA GENERAL CARNEIRO - 914 - SOROCABA - SP</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>SOROCABA</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (88 km)</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (88 km)</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>S05188 - FRIGELAR - RUA GUATEMALA - 371 - RIO DE JANEIRO - RJ</t>
+          <t>S01623 - CLIMA RIO - RUA COMENDADOR OTTERER - 563 - SOROCABA - SP</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -10162,37 +10162,37 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>SOROCABA</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (6 km)</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (6 km)</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>S00895 - FRIGELAR - RUA GENERAL ARGOLO - 15 - SAO CRISTOVAO - RJ</t>
+          <t>S04530 - FRIGELAR - AVENIDA DOUTOR PAULO DE MORAES - 1111 - PIRACICABA - SP</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -10254,27 +10254,27 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>PIRACICABA</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>55 min (67 km)</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>55 min (67 km)</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>S00228 - CLIMA RIO - AVENIDA LOBO JUNIOR - 1184 - RIO DE JANEIRO - RJ</t>
+          <t>S03839 - CLIMA RIO - AVENIDA GOVERNADOR PEDRO TOLEDO - 671 - CAMPINAS - SP</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -10341,12 +10341,12 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>CAMPINAS</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -10356,17 +10356,17 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>55 min (67 km)</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>55 min (67 km)</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>S06150 - FRIGELAR - AVENIDA AYRTON SENNA - 4701 - RIO DE JANEIRO - RJ</t>
+          <t>S01623 - CLIMA RIO - RUA COMENDADOR OTTERER - 563 - SOROCABA - SP</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -10423,32 +10423,32 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>SOROCABA</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (88 km)</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (88 km)</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -10480,12 +10480,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>S00135 - CENTRAL AR - AV. DAS AMERICAS - 18000 - RIO DE JANEIRO - RJ</t>
+          <t>S05854 - FRIGELAR - AVENIDA GENERAL CARNEIRO - 914 - SOROCABA - SP</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -10510,32 +10510,32 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>CENTRAL AR</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>SOROCABA</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (6 km)</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (6 km)</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -10567,12 +10567,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>S06150 - FRIGELAR - AVENIDA AYRTON SENNA - 4701 - RIO DE JANEIRO - RJ</t>
+          <t>S05854 - FRIGELAR - AVENIDA GENERAL CARNEIRO - 914 - SOROCABA - SP</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -10602,27 +10602,27 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>SOROCABA</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (88 km)</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (88 km)</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -10654,12 +10654,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SPI_1</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>S00157 - CLIMA RIO - AVENIDA AYRTON SENNA - 1850 - RIO DE JANEIRO - RJ</t>
+          <t>S01623 - CLIMA RIO - RUA COMENDADOR OTTERER - 563 - SOROCABA - SP</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -10689,27 +10689,27 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>SOROCABA</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (6 km)</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (6 km)</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>S07202 - FRIGELAR - AVENIDA INCONFIDENCIA - 31 - CANOAS - RS</t>
+          <t>S04053 - CLIMA RIO - RUA MIGUEL DE FRIAS - 254 - NITEROI - RJ</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -10822,22 +10822,22 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>CANOAS</t>
+          <t>NITEROI</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>S19798 - HAVAN - AV FARROUPILHA - 4707 - CANOAS - RS</t>
+          <t>S00164 - CLIMA RIO - RUA MANOEL JOAO GONCALVES - 84 - SAO GONCALO - RJ</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -10909,22 +10909,22 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>CANOAS</t>
+          <t>SAO GONCALO</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -10966,12 +10966,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>S00119 - FRIGELAR - AVENIDA PERNAMBUCO - 2285 - PORTO ALEGRE - RS</t>
+          <t>S00633 - FRIOPECAS - RUA TEIXEIRA RIBEIRO - 275 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -10996,22 +10996,22 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>FRIOPECAS</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>S00127 - WEBCONTINENTAL - TRAVENIDAESSA VENEZUELA 210 NAVENIDAEGANTES - SN - PORTO ALEGRE - RS</t>
+          <t>S05188 - FRIGELAR - RUA GUATEMALA - 371 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -11083,22 +11083,22 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>WEBCONTINENTAL</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -11140,12 +11140,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>S01271 - FRIGELAR - AVENIDA PERNAMBUCO - 2273 - PORTO ALEGRE - RS</t>
+          <t>S00895 - FRIGELAR - RUA GENERAL ARGOLO - 15 - SAO CRISTOVAO - RJ</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -11227,12 +11227,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>S00119 - FRIGELAR - AVENIDA PERNAMBUCO - 2285 - PORTO ALEGRE - RS</t>
+          <t>S00228 - CLIMA RIO - AVENIDA LOBO JUNIOR - 1184 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -11257,17 +11257,17 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -11314,12 +11314,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>S18040 - HAVAN - AVENIDA ASSIS BRASIL - 11120 - PORTO ALEGRE - RS</t>
+          <t>S06150 - FRIGELAR - AVENIDA AYRTON SENNA - 4701 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -11344,22 +11344,22 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>S07717 - FRIGELAR - RUA VINTE E CINCO DE JULHO - 536 - NOVO HAMBURGO - RS</t>
+          <t>S00157 - CLIMA RIO - AVENIDA AYRTON SENNA - 1850 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -11431,17 +11431,17 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>NOVO HAMBURGO</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -11488,12 +11488,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>S01271 - FRIGELAR - AVENIDA PERNAMBUCO - 2273 - PORTO ALEGRE - RS</t>
+          <t>S06150 - FRIGELAR - AVENIDA AYRTON SENNA - 4701 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -11523,17 +11523,17 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -11575,12 +11575,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>S02352 - CLIMA RIO - AVENIDA FRANCA - 606 - PORTO ALEGRE - RS</t>
+          <t>S00135 - CENTRAL AR - AV. DAS AMERICAS - 18000 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -11605,17 +11605,17 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>CENTRAL AR</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>S07202 - FRIGELAR - AVENIDA INCONFIDENCIA - 31 - CANOAS - RS</t>
+          <t>S04053 - CLIMA RIO - RUA MIGUEL DE FRIAS - 254 - NITEROI - RJ</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -11692,22 +11692,22 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>CANOAS</t>
+          <t>NITEROI</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -11749,12 +11749,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>S19798 - HAVAN - AV FARROUPILHA - 4707 - CANOAS - RS</t>
+          <t>S00164 - CLIMA RIO - RUA MANOEL JOAO GONCALVES - 84 - SAO GONCALO - RJ</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -11779,22 +11779,22 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>CANOAS</t>
+          <t>SAO GONCALO</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>S00119 - FRIGELAR - AVENIDA PERNAMBUCO - 2285 - PORTO ALEGRE - RS</t>
+          <t>S00633 - FRIOPECAS - RUA TEIXEIRA RIBEIRO - 275 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -11866,22 +11866,22 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>FRIOPECAS</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -11923,12 +11923,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>S00127 - WEBCONTINENTAL - TRAVENIDAESSA VENEZUELA 210 NAVENIDAEGANTES - SN - PORTO ALEGRE - RS</t>
+          <t>S05188 - FRIGELAR - RUA GUATEMALA - 371 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -11953,22 +11953,22 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>WEBCONTINENTAL</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>S15962 - HAVAN - RUA OTAVIO SCHEMES - 4105 - GRAVATAI - RS</t>
+          <t>S00895 - FRIGELAR - RUA GENERAL ARGOLO - 15 - SAO CRISTOVAO - RJ</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -12040,22 +12040,22 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>GRAVATAI</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>S18040 - HAVAN - AVENIDA ASSIS BRASIL - 11120 - PORTO ALEGRE - RS</t>
+          <t>S00228 - CLIMA RIO - AVENIDA LOBO JUNIOR - 1184 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -12127,22 +12127,22 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>S18040 - HAVAN - AVENIDA ASSIS BRASIL - 11120 - PORTO ALEGRE - RS</t>
+          <t>S06150 - FRIGELAR - AVENIDA AYRTON SENNA - 4701 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -12214,22 +12214,22 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -12271,12 +12271,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>S07717 - FRIGELAR - RUA VINTE E CINCO DE JULHO - 536 - NOVO HAMBURGO - RS</t>
+          <t>S00157 - CLIMA RIO - AVENIDA AYRTON SENNA - 1850 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -12301,17 +12301,17 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>NOVO HAMBURGO</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -12358,12 +12358,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>S01271 - FRIGELAR - AVENIDA PERNAMBUCO - 2273 - PORTO ALEGRE - RS</t>
+          <t>S06150 - FRIGELAR - AVENIDA AYRTON SENNA - 4701 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -12393,17 +12393,17 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>S02352 - CLIMA RIO - AVENIDA FRANCA - 606 - PORTO ALEGRE - RS</t>
+          <t>S00135 - CENTRAL AR - AV. DAS AMERICAS - 18000 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -12475,17 +12475,17 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>CENTRAL AR</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -12532,12 +12532,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>S07202 - FRIGELAR - AVENIDA INCONFIDENCIA - 31 - CANOAS - RS</t>
+          <t>S04053 - CLIMA RIO - RUA MIGUEL DE FRIAS - 254 - NITEROI - RJ</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -12562,22 +12562,22 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>CANOAS</t>
+          <t>NITEROI</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>S19798 - HAVAN - AV FARROUPILHA - 4707 - CANOAS - RS</t>
+          <t>S00164 - CLIMA RIO - RUA MANOEL JOAO GONCALVES - 84 - SAO GONCALO - RJ</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -12649,22 +12649,22 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>CANOAS</t>
+          <t>SAO GONCALO</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -12706,12 +12706,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>S00119 - FRIGELAR - AVENIDA PERNAMBUCO - 2285 - PORTO ALEGRE - RS</t>
+          <t>S00633 - FRIOPECAS - RUA TEIXEIRA RIBEIRO - 275 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -12736,22 +12736,22 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>FRIOPECAS</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -12813,7 +12813,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>S00127 - WEBCONTINENTAL - TRAVENIDAESSA VENEZUELA 210 NAVENIDAEGANTES - SN - PORTO ALEGRE - RS</t>
+          <t>S05188 - FRIGELAR - RUA GUATEMALA - 371 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -12823,22 +12823,22 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>WEBCONTINENTAL</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>S01271 - FRIGELAR - AVENIDA PERNAMBUCO - 2273 - PORTO ALEGRE - RS</t>
+          <t>S00895 - FRIGELAR - RUA GENERAL ARGOLO - 15 - SAO CRISTOVAO - RJ</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -12967,12 +12967,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>S00119 - FRIGELAR - AVENIDA PERNAMBUCO - 2285 - PORTO ALEGRE - RS</t>
+          <t>S00228 - CLIMA RIO - AVENIDA LOBO JUNIOR - 1184 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -12997,17 +12997,17 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -13054,12 +13054,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>S01271 - FRIGELAR - AVENIDA PERNAMBUCO - 2273 - PORTO ALEGRE - RS</t>
+          <t>S06150 - FRIGELAR - AVENIDA AYRTON SENNA - 4701 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -13140,17 +13140,17 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -13192,12 +13192,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>S02352 - CLIMA RIO - AVENIDA FRANCA - 606 - PORTO ALEGRE - RS</t>
+          <t>S00157 - CLIMA RIO - AVENIDA AYRTON SENNA - 1850 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -13227,12 +13227,12 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -13279,12 +13279,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>S07202 - FRIGELAR - AVENIDA INCONFIDENCIA - 31 - CANOAS - RS</t>
+          <t>S04053 - CLIMA RIO - RUA MIGUEL DE FRIAS - 254 - NITEROI - RJ</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -13309,22 +13309,22 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>CANOAS</t>
+          <t>NITEROI</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>S19798 - HAVAN - AV FARROUPILHA - 4707 - CANOAS - RS</t>
+          <t>S00164 - CLIMA RIO - RUA MANOEL JOAO GONCALVES - 84 - SAO GONCALO - RJ</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -13396,22 +13396,22 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>CANOAS</t>
+          <t>SAO GONCALO</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -13453,12 +13453,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>S00119 - FRIGELAR - AVENIDA PERNAMBUCO - 2285 - PORTO ALEGRE - RS</t>
+          <t>S00633 - FRIOPECAS - RUA TEIXEIRA RIBEIRO - 275 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -13483,22 +13483,22 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>FRIOPECAS</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -13540,12 +13540,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>S00127 - WEBCONTINENTAL - TRAVENIDAESSA VENEZUELA 210 NAVENIDAEGANTES - SN - PORTO ALEGRE - RS</t>
+          <t>S05188 - FRIGELAR - RUA GUATEMALA - 371 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -13570,22 +13570,22 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>WEBCONTINENTAL</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -13627,12 +13627,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>S15962 - HAVAN - RUA OTAVIO SCHEMES - 4105 - GRAVATAI - RS</t>
+          <t>S00895 - FRIGELAR - RUA GENERAL ARGOLO - 15 - SAO CRISTOVAO - RJ</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -13657,22 +13657,22 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>GRAVATAI</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -13714,12 +13714,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>S18040 - HAVAN - AVENIDA ASSIS BRASIL - 11120 - PORTO ALEGRE - RS</t>
+          <t>S00228 - CLIMA RIO - AVENIDA LOBO JUNIOR - 1184 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -13744,22 +13744,22 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>S18040 - HAVAN - AVENIDA ASSIS BRASIL - 11120 - PORTO ALEGRE - RS</t>
+          <t>S06150 - FRIGELAR - AVENIDA AYRTON SENNA - 4701 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -13831,22 +13831,22 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>FRIGELAR</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>S07717 - FRIGELAR - RUA VINTE E CINCO DE JULHO - 536 - NOVO HAMBURGO - RS</t>
+          <t>S00135 - CENTRAL AR - AV. DAS AMERICAS - 18000 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -13918,17 +13918,17 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CENTRAL AR</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>NOVO HAMBURGO</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -13975,12 +13975,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -13995,7 +13995,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>S01271 - FRIGELAR - AVENIDA PERNAMBUCO - 2273 - PORTO ALEGRE - RS</t>
+          <t>S06150 - FRIGELAR - AVENIDA AYRTON SENNA - 4701 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -14010,17 +14010,17 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>SUL_1</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>S02352 - CLIMA RIO - AVENIDA FRANCA - 606 - PORTO ALEGRE - RS</t>
+          <t>S00157 - CLIMA RIO - AVENIDA AYRTON SENNA - 1850 - RIO DE JANEIRO - RJ</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -14097,12 +14097,12 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -14347,7 +14347,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -14394,7 +14394,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>S02324 - FRIGELAR - ALAMEDA GLETE - 908 - SAO PAULO - SP</t>
+          <t>S00700 - BHP - AV. SENADOR PINHEIRO MACHADO - 22 - SANTOS - SP</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -14404,12 +14404,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -14419,7 +14419,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -14481,7 +14481,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>S00461 - FRIGELAR - ALAMEDA GLETE - 771 - SAO PAULO - SP</t>
+          <t>S00157 - CLIMA RIO - RUA COMENDADOR JOAO BATISTA GLEREAN - SN - PRAIA GRANDE - SP</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -14491,12 +14491,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>PRAIA GRANDE</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -14506,7 +14506,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -15217,7 +15217,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>S02324 - FRIGELAR - ALAMEDA GLETE - 908 - SAO PAULO - SP</t>
+          <t>S01704 - CLIMA RIO - RUA PARAIBUNA - 667 - SAO JOSE DOS CAMPOS - SP</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -15274,12 +15274,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>SAO JOSE DOS CAMPOS</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>S05935 - FRIGELAR - RUA QUIRINO DOS SANTOS - 167 - SAO PAULO - SP</t>
+          <t>S01082 - A.DIAS - AVENIDA CASSIANO RICARDO 521 - SN - SAO JOSE DOS CAMPOS - SP</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -15361,12 +15361,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>A.DIAS</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>SAO JOSE DOS CAMPOS</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -16087,7 +16087,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>S02324 - FRIGELAR - ALAMEDA GLETE - 908 - SAO PAULO - SP</t>
+          <t>S00160 - CENTRAL AR - SANTOS/SP</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -16144,12 +16144,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CENTRAL AR</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -16221,7 +16221,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>S00461 - FRIGELAR - ALAMEDA GLETE - 771 - SAO PAULO - SP</t>
+          <t>S00191 - A.DIAS - AVENIDA PRESIDENTE COSTA E SILVA - 609 - PRAIA GRANDE - SP</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>A.DIAS</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>PRAIA GRANDE</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -16246,7 +16246,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -16435,7 +16435,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -16834,7 +16834,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -16881,7 +16881,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>S02324 - FRIGELAR - ALAMEDA GLETE - 908 - SAO PAULO - SP</t>
+          <t>S01704 - CLIMA RIO - RUA PARAIBUNA - 667 - SAO JOSE DOS CAMPOS - SP</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -16891,12 +16891,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>CLIMA RIO</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>SAO JOSE DOS CAMPOS</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -16906,7 +16906,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>S05935 - FRIGELAR - RUA QUIRINO DOS SANTOS - 167 - SAO PAULO - SP</t>
+          <t>S01082 - A.DIAS - AVENIDA CASSIANO RICARDO 521 - SN - SAO JOSE DOS CAMPOS - SP</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -16978,12 +16978,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>A.DIAS</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>SAO JOSE DOS CAMPOS</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -16993,7 +16993,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -17182,7 +17182,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -17613,7 +17613,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GIOVANNA MENDES</t>
+          <t>LUIZ FALCAO DE SOUZA NETO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -17627,16 +17627,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3175</v>
+        <v>1267</v>
       </c>
       <c r="E2" t="n">
-        <v>2540</v>
+        <v>1013.52</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2540</v>
+        <v>1013.52</v>
       </c>
       <c r="H2" t="n">
         <v>38</v>
@@ -17655,7 +17655,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LUIZ FALCAO DE SOUZA NETO</t>
+          <t>MARCIO JOSE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -17669,16 +17669,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1267</v>
+        <v>794</v>
       </c>
       <c r="E3" t="n">
-        <v>1013.52</v>
+        <v>635.2</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1013.52</v>
+        <v>635.2</v>
       </c>
       <c r="H3" t="n">
         <v>38</v>
@@ -17697,7 +17697,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DIOGO DO NASCIMENTO SANTOS</t>
+          <t>GIOVANNA MENDES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -17711,16 +17711,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>862</v>
+        <v>3175</v>
       </c>
       <c r="E4" t="n">
-        <v>689.6</v>
+        <v>2540</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>689.6</v>
+        <v>2540</v>
       </c>
       <c r="H4" t="n">
         <v>38</v>
@@ -17739,7 +17739,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MARCIO JOSE FLORES PEREIRA</t>
+          <t>DIOGO DO NASCIMENTO SANTOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -17753,16 +17753,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>794</v>
+        <v>862</v>
       </c>
       <c r="E5" t="n">
-        <v>635.2</v>
+        <v>689.6</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>635.2</v>
+        <v>689.6</v>
       </c>
       <c r="H5" t="n">
         <v>38</v>

--- a/public/Journey Novembro 2026 - Opcao 2.xlsx
+++ b/public/Journey Novembro 2026 - Opcao 2.xlsx
@@ -602,24 +602,24 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>GUARULHOS</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -637,7 +637,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -689,24 +689,24 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -719,12 +719,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>BHP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SANTOS</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -811,7 +811,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -863,24 +863,24 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>PRAIA GRANDE</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -893,12 +893,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -950,24 +950,24 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -985,7 +985,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1037,24 +1037,24 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SAO BERNARDO DO CAMPO</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1124,24 +1124,24 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>OSASCO</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1211,24 +1211,24 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1298,24 +1298,24 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1385,24 +1385,24 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>FRIOPECAS</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1472,24 +1472,24 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>GUARULHOS</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1559,24 +1559,24 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1646,24 +1646,24 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>SAO JOSE DOS CAMPOS</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1733,24 +1733,24 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>A.DIAS</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>SAO JOSE DOS CAMPOS</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -1763,12 +1763,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A.DIAS</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1820,24 +1820,24 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1907,24 +1907,24 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>SAO BERNARDO DO CAMPO</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1994,24 +1994,24 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>OSASCO</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2081,24 +2081,24 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2168,24 +2168,24 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2255,24 +2255,24 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>FRIOPECAS</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -2285,12 +2285,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2342,24 +2342,24 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>GUARULHOS</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2429,24 +2429,24 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -2459,12 +2459,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2516,24 +2516,24 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>CENTRAL AR</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>SANTOS</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CENTRAL AR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2603,24 +2603,24 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>A.DIAS</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>PRAIA GRANDE</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -2633,12 +2633,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A.DIAS</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2690,24 +2690,24 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2777,24 +2777,24 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>SAO BERNARDO DO CAMPO</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -2807,12 +2807,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2919,24 +2919,24 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3006,24 +3006,24 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t>FRIOPECAS</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -3036,12 +3036,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3093,24 +3093,24 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>GUARULHOS</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3180,24 +3180,24 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -3210,12 +3210,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3267,24 +3267,24 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>SAO JOSE DOS CAMPOS</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3354,24 +3354,24 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t>A.DIAS</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
           <t>SAO JOSE DOS CAMPOS</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -3384,12 +3384,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>A.DIAS</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3441,24 +3441,24 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3528,24 +3528,24 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
           <t>SAO BERNARDO DO CAMPO</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M37" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3615,24 +3615,24 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>OSASCO</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M38" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3702,24 +3702,24 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -3732,12 +3732,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3789,24 +3789,24 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3876,24 +3876,24 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
+          <t>FRIOPECAS</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>SPC1</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -4018,24 +4018,24 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
           <t>JOAO PESSOA</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -4105,24 +4105,24 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
+          <t>MAGNO</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
           <t>CABEDELO</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -4135,12 +4135,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>MAGNO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -4192,24 +4192,24 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
+          <t>FRIOPECAS</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -4279,24 +4279,24 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4366,24 +4366,24 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
+          <t>FERREIRA COSTA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M47" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>FERREIRA COSTA</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -4453,24 +4453,24 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M48" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4540,24 +4540,24 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4627,24 +4627,24 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
+          <t>FERREIRA COSTA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>FERREIRA COSTA</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4714,24 +4714,24 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K51" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K52" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -4831,12 +4831,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -4888,24 +4888,24 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
           <t>JOAO PESSOA</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K53" t="inlineStr">
         <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -4923,12 +4923,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>Viagem</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -4975,24 +4975,24 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
           <t>JOAO PESSOA</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K54" t="inlineStr">
         <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M54" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -5005,17 +5005,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>Viagem</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -5062,24 +5062,24 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
+          <t>FRIOPECAS</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K55" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -5149,24 +5149,24 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K56" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -5179,12 +5179,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -5236,24 +5236,24 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
+          <t>FERREIRA COSTA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K57" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>FERREIRA COSTA</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -5323,24 +5323,24 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M58" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -5353,12 +5353,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -5410,24 +5410,24 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K59" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M59" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5497,24 +5497,24 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
+          <t>FERREIRA COSTA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K60" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M60" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>FERREIRA COSTA</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5584,24 +5584,24 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K61" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -5671,24 +5671,24 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K62" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -5701,12 +5701,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5758,24 +5758,24 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
+          <t>FERREIRA COSTA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K63" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>FERREIRA COSTA</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -5845,24 +5845,24 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K64" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -5875,12 +5875,12 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -5932,24 +5932,24 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
+          <t>FRIOPECAS</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K65" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -6019,24 +6019,24 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K66" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -6106,24 +6106,24 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
+          <t>FERREIRA COSTA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K67" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>FERREIRA COSTA</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -6193,24 +6193,24 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K68" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -6223,12 +6223,12 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -6335,24 +6335,24 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K70" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M70" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -6422,24 +6422,24 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K71" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -6452,12 +6452,12 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -6509,24 +6509,24 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
+          <t>FRIOPECAS</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K72" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -6596,24 +6596,24 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
+          <t>FERREIRA COSTA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K73" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M73" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -6626,12 +6626,12 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>FERREIRA COSTA</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -6683,24 +6683,24 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
           <t>JOAO PESSOA</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K74" t="inlineStr">
         <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -6718,12 +6718,12 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Viagem</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -6770,24 +6770,24 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
+          <t>MAGNO</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
           <t>CABEDELO</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K75" t="inlineStr">
         <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M75" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -6800,17 +6800,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>MAGNO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>Viagem</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -6857,24 +6857,24 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
+          <t>FERREIRA COSTA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K76" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M76" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>FERREIRA COSTA</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -6944,24 +6944,24 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K77" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -7031,24 +7031,24 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K78" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M78" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -7118,24 +7118,24 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
+          <t>FERREIRA COSTA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K79" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M79" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -7148,12 +7148,12 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>FERREIRA COSTA</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -7205,24 +7205,24 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K80" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M80" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -7292,24 +7292,24 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>NE_2</t>
-        </is>
-      </c>
       <c r="K81" t="inlineStr">
         <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M81" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -7322,12 +7322,12 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -7434,24 +7434,24 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
           <t>CANOAS</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K83" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M83" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -7521,24 +7521,24 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
           <t>CANOAS</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K84" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M84" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -7551,12 +7551,12 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -7608,24 +7608,24 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
           <t>PORTO ALEGRE</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K85" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M85" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -7695,24 +7695,24 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
+          <t>WEBCONTINENTAL</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
           <t>PORTO ALEGRE</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K86" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -7725,12 +7725,12 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>WEBCONTINENTAL</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -7782,24 +7782,24 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
           <t>PORTO ALEGRE</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K87" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M87" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -7869,24 +7869,24 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
           <t>VIAMAO</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K88" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M88" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -7956,24 +7956,24 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
           <t>PORTO ALEGRE</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K89" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M89" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -8043,24 +8043,24 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
           <t>NOVO HAMBURGO</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K90" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M90" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -8073,12 +8073,12 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -8130,24 +8130,24 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
           <t>PORTO ALEGRE</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K91" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M91" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -8217,24 +8217,24 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
           <t>PORTO ALEGRE</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K92" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M92" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -8247,12 +8247,12 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -8304,24 +8304,24 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
           <t>CANOAS</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K93" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M93" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -8391,24 +8391,24 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
           <t>CANOAS</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K94" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M94" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -8421,12 +8421,12 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -8478,24 +8478,24 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
           <t>PORTO ALEGRE</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K95" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M95" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -8513,7 +8513,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -8565,24 +8565,24 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
+          <t>WEBCONTINENTAL</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
           <t>PORTO ALEGRE</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K96" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M96" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -8595,12 +8595,12 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>WEBCONTINENTAL</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -8652,24 +8652,24 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
           <t>GRAVATAI</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K97" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M97" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -8739,24 +8739,24 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
           <t>VIAMAO</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K98" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M98" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -8769,12 +8769,12 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -8826,24 +8826,24 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
           <t>CANOAS</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K99" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M99" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -8861,7 +8861,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
@@ -8913,24 +8913,24 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
           <t>NOVO HAMBURGO</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K100" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M100" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -8943,12 +8943,12 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -9000,24 +9000,24 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
           <t>PORTO ALEGRE</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K101" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M101" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -9087,24 +9087,24 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
           <t>PORTO ALEGRE</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K102" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M102" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -9174,24 +9174,24 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
           <t>CANOAS</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K103" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M103" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -9261,24 +9261,24 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
           <t>CANOAS</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K104" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M104" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -9291,12 +9291,12 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -9348,24 +9348,24 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
           <t>PORTO ALEGRE</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K105" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M105" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -9435,24 +9435,24 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
+          <t>WEBCONTINENTAL</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
           <t>PORTO ALEGRE</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K106" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M106" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -9465,12 +9465,12 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>WEBCONTINENTAL</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -9522,24 +9522,24 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
           <t>GUAIBA</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K107" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M107" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -9609,24 +9609,24 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
           <t>VIAMAO</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K108" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M108" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -9751,24 +9751,24 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
           <t>PORTO ALEGRE</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K110" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M110" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -9838,24 +9838,24 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
           <t>PORTO ALEGRE</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K111" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M111" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -9925,24 +9925,24 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
           <t>CANOAS</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K112" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M112" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -10012,24 +10012,24 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
           <t>CANOAS</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K113" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M113" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -10099,24 +10099,24 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
           <t>PORTO ALEGRE</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K114" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M114" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
@@ -10186,24 +10186,24 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
+          <t>WEBCONTINENTAL</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
           <t>PORTO ALEGRE</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K115" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M115" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -10216,12 +10216,12 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>WEBCONTINENTAL</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
@@ -10273,24 +10273,24 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
           <t>GRAVATAI</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K116" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M116" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -10360,24 +10360,24 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
           <t>VIAMAO</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K117" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M117" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -10390,12 +10390,12 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
@@ -10447,24 +10447,24 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
           <t>CANOAS</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K118" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M118" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -10482,7 +10482,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
@@ -10534,24 +10534,24 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
           <t>NOVO HAMBURGO</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K119" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M119" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -10621,24 +10621,24 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
           <t>PORTO ALEGRE</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K120" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M120" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -10708,24 +10708,24 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
           <t>PORTO ALEGRE</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>SUL_1</t>
-        </is>
-      </c>
       <c r="K121" t="inlineStr">
         <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M121" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -10738,12 +10738,12 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -10850,32 +10850,32 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
           <t>HORTOLANDIA</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K123" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="M123" t="inlineStr">
         <is>
           <t>20 min (8 km)</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>20 min (8 km)</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
@@ -10937,42 +10937,42 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
           <t>SUMARE</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K124" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="M124" t="inlineStr">
         <is>
           <t>15 min (5 km)</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
@@ -11024,32 +11024,32 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
           <t>SOROCABA</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K125" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t>1h15 (88 km)</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (88 km)</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -11111,42 +11111,42 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
           <t>SOROCABA</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K126" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
+      <c r="M126" t="inlineStr">
         <is>
           <t>15 min (6 km)</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (6 km)</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -11198,32 +11198,32 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
           <t>PIRACICABA</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K127" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
+      <c r="M127" t="inlineStr">
         <is>
           <t>55 min (67 km)</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>55 min (67 km)</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
@@ -11285,42 +11285,42 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
+          <t>CENTRAL AR</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
           <t>ITU</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K128" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="M128" t="inlineStr">
         <is>
           <t>1h15 (98 km)</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (98 km)</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>CENTRAL AR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -11372,32 +11372,32 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
           <t>CAMPINAS</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K129" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="M129" t="inlineStr">
         <is>
           <t>15 min (5 km)</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -11459,42 +11459,42 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
           <t>CAMPINAS</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K130" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
+      <c r="M130" t="inlineStr">
         <is>
           <t>15 min (5 km)</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -11546,32 +11546,32 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
           <t>SOROCABA</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K131" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
+      <c r="M131" t="inlineStr">
         <is>
           <t>1h15 (88 km)</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (88 km)</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -11633,42 +11633,42 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
           <t>SOROCABA</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K132" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
+      <c r="M132" t="inlineStr">
         <is>
           <t>15 min (6 km)</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (6 km)</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
@@ -11720,32 +11720,32 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
+          <t>BHP</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
           <t>CAMPINAS</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K133" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="M133" t="inlineStr">
         <is>
           <t>20 min (8 km)</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>20 min (8 km)</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -11755,7 +11755,7 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -11807,42 +11807,42 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
           <t>CAMPINAS</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K134" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
+      <c r="M134" t="inlineStr">
         <is>
           <t>15 min (5 km)</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -11894,32 +11894,32 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
+          <t>CENTRAL AR</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
           <t>ARACATUBA</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K135" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
+      <c r="M135" t="inlineStr">
         <is>
           <t>Voo Aéreo / Deslocamento Local (5 km)</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Voo Aéreo / Deslocamento Local (5 km)</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>CENTRAL AR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -11981,42 +11981,42 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
           <t>ARACATUBA</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K136" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
+      <c r="M136" t="inlineStr">
         <is>
           <t>10 min (4 km)</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>10 min (4 km)</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
@@ -12068,32 +12068,32 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
           <t>RIBEIRAO PRETO</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K137" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t>2h10 (173 km)</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>2h10 (173 km)</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -12103,7 +12103,7 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
@@ -12155,42 +12155,42 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
           <t>RIBEIRAO PRETO</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K138" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
+      <c r="M138" t="inlineStr">
         <is>
           <t>10 min (2 km)</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>10 min (2 km)</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
@@ -12242,32 +12242,32 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
+          <t>CENTRAL AR</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
           <t>ITU</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K139" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
+      <c r="M139" t="inlineStr">
         <is>
           <t>45 min (52 km)</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>45 min (52 km)</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>CENTRAL AR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -12329,42 +12329,42 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
           <t>INDAIATUBA</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K140" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
+      <c r="M140" t="inlineStr">
         <is>
           <t>45 min (52 km)</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>45 min (52 km)</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -12416,24 +12416,24 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
           <t>SOROCABA</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K141" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M141" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -12503,24 +12503,24 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
           <t>SOROCABA</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K142" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M142" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -12533,12 +12533,12 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
@@ -12590,32 +12590,32 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
           <t>CAMPINAS</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K143" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
+      <c r="M143" t="inlineStr">
         <is>
           <t>20 min (8 km)</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>20 min (8 km)</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
@@ -12677,42 +12677,42 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
           <t>CAMPINAS</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K144" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
+      <c r="M144" t="inlineStr">
         <is>
           <t>15 min (5 km)</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
@@ -12764,32 +12764,32 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
           <t>LIMEIRA</t>
         </is>
       </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K145" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
+      <c r="M145" t="inlineStr">
         <is>
           <t>20 min (8 km)</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>20 min (8 km)</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
@@ -12851,42 +12851,42 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
           <t>SANTA BARBARA D OESTE</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K146" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
+      <c r="M146" t="inlineStr">
         <is>
           <t>15 min (5 km)</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
           <t>SOROCABA</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K147" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
+      <c r="M147" t="inlineStr">
         <is>
           <t>1h15 (88 km)</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (88 km)</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -12973,7 +12973,7 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
@@ -13025,42 +13025,42 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
           <t>SOROCABA</t>
         </is>
       </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K148" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
+      <c r="M148" t="inlineStr">
         <is>
           <t>15 min (6 km)</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (6 km)</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
@@ -13167,32 +13167,32 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
           <t>RIBEIRAO PRETO</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K150" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
+      <c r="M150" t="inlineStr">
         <is>
           <t>2h10 (173 km)</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>2h10 (173 km)</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
@@ -13254,42 +13254,42 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
           <t>RIBEIRAO PRETO</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K151" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
+      <c r="M151" t="inlineStr">
         <is>
           <t>10 min (2 km)</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>10 min (2 km)</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
@@ -13341,32 +13341,32 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
           <t>CAMPINAS</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K152" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t>20 min (8 km)</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>20 min (8 km)</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
@@ -13428,42 +13428,42 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
           <t>CAMPINAS</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K153" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
+      <c r="M153" t="inlineStr">
         <is>
           <t>15 min (5 km)</t>
         </is>
       </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (5 km)</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
@@ -13515,32 +13515,32 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
+          <t>BHP</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
           <t>SOROCABA</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K154" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
+      <c r="M154" t="inlineStr">
         <is>
           <t>1h15 (88 km)</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (88 km)</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
@@ -13602,42 +13602,42 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
+          <t>HAVAN</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
           <t>SOROCABA</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K155" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr">
+      <c r="M155" t="inlineStr">
         <is>
           <t>15 min (6 km)</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (6 km)</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>HAVAN</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
@@ -13689,32 +13689,32 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
           <t>PIRACICABA</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K156" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
+      <c r="M156" t="inlineStr">
         <is>
           <t>55 min (67 km)</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>55 min (67 km)</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
@@ -13776,42 +13776,42 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
           <t>CAMPINAS</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K157" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
+      <c r="M157" t="inlineStr">
         <is>
           <t>55 min (67 km)</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>55 min (67 km)</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
@@ -13863,32 +13863,32 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
           <t>CAMPINAS</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K158" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
+      <c r="M158" t="inlineStr">
         <is>
           <t>1h15 (88 km)</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (88 km)</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -13898,7 +13898,7 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
@@ -13950,42 +13950,42 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
+          <t>BHP</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
           <t>CAMPINAS</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K159" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr">
+      <c r="M159" t="inlineStr">
         <is>
           <t>15 min (6 km)</t>
         </is>
       </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (6 km)</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
@@ -14037,32 +14037,32 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
           <t>SOROCABA</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K160" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr">
+      <c r="M160" t="inlineStr">
         <is>
           <t>1h15 (88 km)</t>
         </is>
       </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>1h15 (88 km)</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
@@ -14124,42 +14124,42 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
           <t>SOROCABA</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>SPI_1</t>
-        </is>
-      </c>
       <c r="K161" t="inlineStr">
         <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
+      <c r="M161" t="inlineStr">
         <is>
           <t>15 min (6 km)</t>
         </is>
       </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>15 min (6 km)</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
@@ -14266,24 +14266,24 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
           <t>NITEROI</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr">
+      <c r="K163" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
+      <c r="L163" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M163" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
@@ -14353,24 +14353,24 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
           <t>SAO GONCALO</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr">
+      <c r="K164" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
+      <c r="L164" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M164" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -14383,12 +14383,12 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
@@ -14440,24 +14440,24 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
+          <t>FRIOPECAS</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J165" t="inlineStr">
+      <c r="K165" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
+      <c r="L165" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M165" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -14475,7 +14475,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
@@ -14527,24 +14527,24 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J166" t="inlineStr">
+      <c r="K166" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
+      <c r="L166" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M166" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -14557,12 +14557,12 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
@@ -14614,24 +14614,24 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J167" t="inlineStr">
+      <c r="K167" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="L167" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M167" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
@@ -14701,24 +14701,24 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr">
+      <c r="K168" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
+      <c r="L168" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M168" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -14731,12 +14731,12 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
@@ -14788,24 +14788,24 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J169" t="inlineStr">
+      <c r="K169" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
+      <c r="L169" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M169" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
@@ -14875,24 +14875,24 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr">
+      <c r="K170" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
+      <c r="L170" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M170" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -14905,12 +14905,12 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
@@ -14962,24 +14962,24 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J171" t="inlineStr">
+      <c r="K171" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
+      <c r="L171" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M171" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -14997,7 +14997,7 @@
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
@@ -15049,24 +15049,24 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
+          <t>CENTRAL AR</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr">
+      <c r="K172" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
+      <c r="L172" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M172" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -15079,12 +15079,12 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>CENTRAL AR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
@@ -15136,24 +15136,24 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
           <t>NITEROI</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr">
+      <c r="K173" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
+      <c r="L173" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M173" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
@@ -15223,24 +15223,24 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
           <t>SAO GONCALO</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr">
+      <c r="K174" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
+      <c r="L174" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M174" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -15253,12 +15253,12 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
@@ -15310,24 +15310,24 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
+          <t>FRIOPECAS</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J175" t="inlineStr">
+      <c r="K175" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
+      <c r="L175" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M175" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
@@ -15397,24 +15397,24 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J176" t="inlineStr">
+      <c r="K176" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
+      <c r="L176" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M176" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -15427,12 +15427,12 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
@@ -15484,24 +15484,24 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr">
+      <c r="K177" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
+      <c r="L177" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M177" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -15519,7 +15519,7 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q177" t="inlineStr">
@@ -15571,24 +15571,24 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr">
+      <c r="K178" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
+      <c r="L178" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M178" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -15601,12 +15601,12 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
@@ -15658,24 +15658,24 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
+          <t>FRIOPECAS</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr">
+      <c r="K179" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
+      <c r="L179" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M179" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
@@ -15745,24 +15745,24 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr">
+      <c r="K180" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
+      <c r="L180" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M180" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -15775,12 +15775,12 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
@@ -15832,24 +15832,24 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J181" t="inlineStr">
+      <c r="K181" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
+      <c r="L181" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M181" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -15867,7 +15867,7 @@
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
@@ -15919,24 +15919,24 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
+          <t>CENTRAL AR</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J182" t="inlineStr">
+      <c r="K182" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
+      <c r="L182" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M182" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -15949,12 +15949,12 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>CENTRAL AR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
@@ -16006,24 +16006,24 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
           <t>NITEROI</t>
         </is>
       </c>
-      <c r="J183" t="inlineStr">
+      <c r="K183" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
+      <c r="L183" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M183" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
@@ -16093,24 +16093,24 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
           <t>SAO GONCALO</t>
         </is>
       </c>
-      <c r="J184" t="inlineStr">
+      <c r="K184" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
+      <c r="L184" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M184" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -16123,12 +16123,12 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
@@ -16180,24 +16180,24 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
+          <t>FRIOPECAS</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J185" t="inlineStr">
+      <c r="K185" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
+      <c r="L185" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M185" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -16215,7 +16215,7 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
@@ -16267,24 +16267,24 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J186" t="inlineStr">
+      <c r="K186" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
+      <c r="L186" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M186" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -16297,12 +16297,12 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
@@ -16354,24 +16354,24 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J187" t="inlineStr">
+      <c r="K187" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
+      <c r="L187" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M187" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -16389,7 +16389,7 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
@@ -16441,24 +16441,24 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J188" t="inlineStr">
+      <c r="K188" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
+      <c r="L188" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M188" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -16471,12 +16471,12 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
@@ -16583,24 +16583,24 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J190" t="inlineStr">
+      <c r="K190" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
+      <c r="L190" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M190" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -16618,7 +16618,7 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
@@ -16670,24 +16670,24 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
+          <t>CENTRAL AR</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J191" t="inlineStr">
+      <c r="K191" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
+      <c r="L191" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M191" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -16700,12 +16700,12 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>CENTRAL AR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
@@ -16757,24 +16757,24 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
           <t>NITEROI</t>
         </is>
       </c>
-      <c r="J192" t="inlineStr">
+      <c r="K192" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
+      <c r="L192" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M192" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -16792,7 +16792,7 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
@@ -16844,24 +16844,24 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
           <t>SAO GONCALO</t>
         </is>
       </c>
-      <c r="J193" t="inlineStr">
+      <c r="K193" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
+      <c r="L193" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M193" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -16874,12 +16874,12 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
@@ -16931,24 +16931,24 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
+          <t>FRIOPECAS</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J194" t="inlineStr">
+      <c r="K194" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
+      <c r="L194" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M194" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -16966,7 +16966,7 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -17018,24 +17018,24 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J195" t="inlineStr">
+      <c r="K195" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
+      <c r="L195" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M195" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -17048,12 +17048,12 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
@@ -17105,24 +17105,24 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J196" t="inlineStr">
+      <c r="K196" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
+      <c r="L196" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M196" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -17140,7 +17140,7 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
@@ -17192,24 +17192,24 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J197" t="inlineStr">
+      <c r="K197" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
+      <c r="L197" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M197" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -17222,12 +17222,12 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
@@ -17279,24 +17279,24 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
+          <t>FRIOPECAS</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J198" t="inlineStr">
+      <c r="K198" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
+      <c r="L198" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M198" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -17314,7 +17314,7 @@
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>FRIOPECAS</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
@@ -17366,24 +17366,24 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J199" t="inlineStr">
+      <c r="K199" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
+      <c r="L199" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M199" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -17396,12 +17396,12 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
@@ -17453,24 +17453,24 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
+          <t>FRIGELAR</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J200" t="inlineStr">
+      <c r="K200" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
+      <c r="L200" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M200" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -17488,7 +17488,7 @@
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>FRIGELAR</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
@@ -17540,24 +17540,24 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
+          <t>CLIMA RIO</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="J201" t="inlineStr">
+      <c r="K201" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
+      <c r="L201" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>35 min</t>
-        </is>
-      </c>
       <c r="M201" t="inlineStr">
         <is>
           <t>35 min</t>
@@ -17570,12 +17570,12 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>CLIMA RIO</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
@@ -17663,20 +17663,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1276</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1021.04</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1021.04</v>
       </c>
       <c r="H2" t="n">
         <v>38</v>
@@ -17705,20 +17705,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1185</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>947.92</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>947.92</v>
       </c>
       <c r="H3" t="n">
         <v>38</v>
@@ -17747,20 +17747,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>642.48</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>642.48</v>
       </c>
       <c r="H4" t="n">
         <v>38</v>
@@ -17789,20 +17789,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+00:00</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>4036</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3229.2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3229.2</v>
       </c>
       <c r="H5" t="n">
         <v>38</v>
@@ -17831,20 +17831,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+00:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>977</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>781.4400000000001</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>781.4400000000001</v>
       </c>
       <c r="H6" t="n">
         <v>38</v>
